--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6633C2A2-9F00-4942-919B-29D63C4E9B8B}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67098C37-D966-4BF4-91BF-B7E28FD8FF2C}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
+    <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
   <sheets>
     <sheet name="Elec" sheetId="1" r:id="rId1"/>
@@ -612,7 +612,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -635,58 +635,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1039,7 +988,8 @@
     <col min="1" max="1" width="17.73046875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.86328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.86328125" customWidth="1"/>
-    <col min="4" max="4" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -3773,8 +3723,8 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -3818,7 +3768,7 @@
         <v>25003169</v>
       </c>
       <c r="C4" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -3829,7 +3779,7 @@
         <v>25003215</v>
       </c>
       <c r="C5" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -3884,7 +3834,7 @@
         <v>25003200</v>
       </c>
       <c r="C10" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
@@ -3994,7 +3944,7 @@
         <v>25003165</v>
       </c>
       <c r="C20" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
@@ -4049,7 +3999,7 @@
         <v>25003226</v>
       </c>
       <c r="C25" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
@@ -4115,7 +4065,7 @@
         <v>25003181</v>
       </c>
       <c r="C31" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
@@ -4137,7 +4087,7 @@
         <v>25003180</v>
       </c>
       <c r="C33" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
@@ -4291,7 +4241,7 @@
         <v>25003248</v>
       </c>
       <c r="C47" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
@@ -4489,7 +4439,7 @@
         <v>25003290</v>
       </c>
       <c r="C65" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.45">
@@ -4709,7 +4659,7 @@
         <v>25003265</v>
       </c>
       <c r="C85" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.45">
@@ -4742,7 +4692,7 @@
         <v>25003217</v>
       </c>
       <c r="C88" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.45">
@@ -4775,7 +4725,7 @@
         <v>25003256</v>
       </c>
       <c r="C91" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.45">
@@ -4808,7 +4758,7 @@
         <v>25003250</v>
       </c>
       <c r="C94" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.45">
@@ -4830,7 +4780,7 @@
         <v>25003214</v>
       </c>
       <c r="C96" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.45">
@@ -4896,7 +4846,7 @@
         <v>25003247</v>
       </c>
       <c r="C102" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.45">
@@ -5369,7 +5319,7 @@
         <v>25003173</v>
       </c>
       <c r="C145" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.45">

--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67098C37-D966-4BF4-91BF-B7E28FD8FF2C}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9FB7259-DE41-44B7-8893-534D3CAF51D4}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
+    <workbookView xWindow="43080" yWindow="-7455" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
   <sheets>
     <sheet name="Elec" sheetId="1" r:id="rId1"/>
     <sheet name="Gas" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Gas!$A$1:$C$152</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -635,7 +638,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3746,7 +3760,7 @@
         <v>25003273</v>
       </c>
       <c r="C2" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -3757,7 +3771,7 @@
         <v>25003187</v>
       </c>
       <c r="C3" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -3790,7 +3804,7 @@
         <v>25003302</v>
       </c>
       <c r="C6" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -3812,7 +3826,7 @@
         <v>25003167</v>
       </c>
       <c r="C8" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
@@ -3845,7 +3859,7 @@
         <v>25003183</v>
       </c>
       <c r="C11" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
@@ -3878,7 +3892,7 @@
         <v>25003188</v>
       </c>
       <c r="C14" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
@@ -3889,7 +3903,7 @@
         <v>25003184</v>
       </c>
       <c r="C15" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
@@ -3900,7 +3914,7 @@
         <v>25003218</v>
       </c>
       <c r="C16" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
@@ -3911,7 +3925,7 @@
         <v>25003212</v>
       </c>
       <c r="C17" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
@@ -3922,7 +3936,7 @@
         <v>25003164</v>
       </c>
       <c r="C18" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
@@ -3933,7 +3947,7 @@
         <v>25003197</v>
       </c>
       <c r="C19" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
@@ -3955,7 +3969,7 @@
         <v>25000769</v>
       </c>
       <c r="C21" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
@@ -4010,7 +4024,7 @@
         <v>25003228</v>
       </c>
       <c r="C26" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
@@ -4054,7 +4068,7 @@
         <v>25003225</v>
       </c>
       <c r="C30" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
@@ -4076,7 +4090,7 @@
         <v>25003208</v>
       </c>
       <c r="C32" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
@@ -4164,7 +4178,7 @@
         <v>25003207</v>
       </c>
       <c r="C40" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
@@ -4186,7 +4200,7 @@
         <v>25003244</v>
       </c>
       <c r="C42" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
@@ -4208,7 +4222,7 @@
         <v>25003253</v>
       </c>
       <c r="C44" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
@@ -4230,7 +4244,7 @@
         <v>25003201</v>
       </c>
       <c r="C46" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
@@ -5400,6 +5414,9 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B152">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9FB7259-DE41-44B7-8893-534D3CAF51D4}"/>
+  <xr:revisionPtr revIDLastSave="194" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46CF412B-1059-416F-A712-6B96005F6DF0}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-7455" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Gas!$A$1:$C$152</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4112,7 +4113,7 @@
         <v>25003168</v>
       </c>
       <c r="C34" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
@@ -4123,7 +4124,7 @@
         <v>25003191</v>
       </c>
       <c r="C35" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
@@ -4134,7 +4135,7 @@
         <v>25003189</v>
       </c>
       <c r="C36" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
@@ -4156,7 +4157,7 @@
         <v>25003170</v>
       </c>
       <c r="C38" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
@@ -4189,7 +4190,7 @@
         <v>25003229</v>
       </c>
       <c r="C41" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
@@ -4310,7 +4311,7 @@
         <v>25003163</v>
       </c>
       <c r="C52" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.45">

--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="194" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46CF412B-1059-416F-A712-6B96005F6DF0}"/>
+  <xr:revisionPtr revIDLastSave="195" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B7ABC99-927F-4485-B42B-A9BE482410FC}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-7455" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
@@ -4597,7 +4597,7 @@
         <v>25003267</v>
       </c>
       <c r="C78" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.45">

--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="195" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B7ABC99-927F-4485-B42B-A9BE482410FC}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB69F5CA-BD29-479A-B3A7-F2F42047B2AA}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-7455" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
   <sheets>
     <sheet name="Elec" sheetId="1" r:id="rId1"/>
@@ -4168,7 +4168,7 @@
         <v>25003213</v>
       </c>
       <c r="C39" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
@@ -4344,7 +4344,7 @@
         <v>25003298</v>
       </c>
       <c r="C55" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.45">
@@ -4366,7 +4366,7 @@
         <v>25003242</v>
       </c>
       <c r="C57" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.45">
@@ -4377,7 +4377,7 @@
         <v>25003264</v>
       </c>
       <c r="C58" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.45">
@@ -4421,7 +4421,7 @@
         <v>25003294</v>
       </c>
       <c r="C62" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.45">
@@ -4432,7 +4432,7 @@
         <v>25003196</v>
       </c>
       <c r="C63" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.45">
@@ -4465,7 +4465,7 @@
         <v>25003230</v>
       </c>
       <c r="C66" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.45">
@@ -4487,7 +4487,7 @@
         <v>25003198</v>
       </c>
       <c r="C68" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.45">
@@ -4498,7 +4498,7 @@
         <v>25003174</v>
       </c>
       <c r="C69" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.45">
@@ -4520,7 +4520,7 @@
         <v>25003268</v>
       </c>
       <c r="C71" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.45">
@@ -4531,7 +4531,7 @@
         <v>25003300</v>
       </c>
       <c r="C72" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.45">

--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB69F5CA-BD29-479A-B3A7-F2F42047B2AA}"/>
+  <xr:revisionPtr revIDLastSave="349" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BBD25DB-FEAB-45C6-95D4-ABB8C30357C1}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Gas" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Gas!$A$1:$C$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Gas!$A$1:$D$152</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="168">
   <si>
     <t>Stand</t>
   </si>
@@ -539,6 +539,15 @@
   </si>
   <si>
     <t xml:space="preserve">Meter Serial </t>
+  </si>
+  <si>
+    <t>FL03/308</t>
+  </si>
+  <si>
+    <t>FL03/304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date Installed </t>
   </si>
 </sst>
 </file>
@@ -608,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -627,13 +636,8 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3734,1685 +3738,1992 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E65B138-F96C-4BD4-BD5E-9019D6D5FB3F}">
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:D152"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D1" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2">
         <v>25003273</v>
       </c>
-      <c r="C2" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C2" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2">
         <v>25003187</v>
       </c>
-      <c r="C3" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2">
         <v>25003169</v>
       </c>
-      <c r="C4" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2">
         <v>25003215</v>
       </c>
-      <c r="C5" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>25003302</v>
       </c>
-      <c r="C6" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2">
         <v>25003172</v>
       </c>
-      <c r="C7" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="2">
         <v>25003167</v>
       </c>
-      <c r="C8" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="2">
         <v>25003195</v>
       </c>
-      <c r="C9" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="2">
         <v>25003200</v>
       </c>
-      <c r="C10" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="2">
         <v>25003183</v>
       </c>
-      <c r="C11" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="2">
         <v>25003182</v>
       </c>
-      <c r="C12" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="2">
         <v>25003206</v>
       </c>
-      <c r="C13" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="2">
         <v>25003188</v>
       </c>
-      <c r="C14" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="2">
         <v>25003184</v>
       </c>
-      <c r="C15" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="2">
         <v>25003218</v>
       </c>
-      <c r="C16" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="2">
         <v>25003212</v>
       </c>
-      <c r="C17" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="2">
         <v>25003164</v>
       </c>
-      <c r="C18" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="2">
         <v>25003197</v>
       </c>
-      <c r="C19" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="2">
         <v>25003165</v>
       </c>
-      <c r="C20" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="2">
         <v>25000769</v>
       </c>
-      <c r="C21" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="2">
         <v>25003301</v>
       </c>
-      <c r="C22" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="2">
         <v>25003280</v>
       </c>
-      <c r="C23" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B24" s="2">
         <v>25003286</v>
       </c>
-      <c r="C24" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C24" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B25" s="2">
         <v>25003226</v>
       </c>
-      <c r="C25" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B26" s="2">
         <v>25003228</v>
       </c>
-      <c r="C26" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B27" s="2">
         <v>25007138</v>
       </c>
-      <c r="C27" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B28" s="2">
         <v>25003303</v>
       </c>
-      <c r="C28" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C28" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B29" s="2">
         <v>25003222</v>
       </c>
-      <c r="C29" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C29" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="2">
         <v>25003225</v>
       </c>
-      <c r="C30" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" s="5">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B31" s="2">
         <v>25003181</v>
       </c>
-      <c r="C31" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B32" s="2">
         <v>25003208</v>
       </c>
-      <c r="C32" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B33" s="2">
         <v>25003180</v>
       </c>
-      <c r="C33" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B34" s="2">
         <v>25003168</v>
       </c>
-      <c r="C34" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B35" s="2">
         <v>25003191</v>
       </c>
-      <c r="C35" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="2">
         <v>25003189</v>
       </c>
-      <c r="C36" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B37" s="2">
         <v>25003209</v>
       </c>
-      <c r="C37" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B38" s="2">
         <v>25003170</v>
       </c>
-      <c r="C38" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B39" s="2">
         <v>25003213</v>
       </c>
-      <c r="C39" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B40" s="2">
         <v>25003207</v>
       </c>
-      <c r="C40" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D40" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B41" s="2">
         <v>25003229</v>
       </c>
-      <c r="C41" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B42" s="2">
         <v>25003244</v>
       </c>
-      <c r="C42" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B43" s="2">
         <v>25003243</v>
       </c>
-      <c r="C43" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B44" s="2">
         <v>25003253</v>
       </c>
-      <c r="C44" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D44" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B45" s="2">
         <v>25003246</v>
       </c>
-      <c r="C45" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C45" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B46" s="2">
         <v>25003201</v>
       </c>
-      <c r="C46" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B47" s="2">
         <v>25003248</v>
       </c>
-      <c r="C47" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B48" s="2">
         <v>25003205</v>
       </c>
-      <c r="C48" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B49" s="2">
         <v>25003293</v>
       </c>
-      <c r="C49" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B50" s="2">
         <v>25003223</v>
       </c>
-      <c r="C50" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B51" s="2">
         <v>25003199</v>
       </c>
-      <c r="C51" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B52" s="2">
         <v>25003163</v>
       </c>
-      <c r="C52" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D52" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B53" s="2">
         <v>25003216</v>
       </c>
-      <c r="C53" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B54" s="2">
         <v>25003289</v>
       </c>
-      <c r="C54" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C54" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D54" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B55" s="2">
         <v>25003298</v>
       </c>
-      <c r="C55" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C55" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D55" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B56" s="2">
         <v>25003292</v>
       </c>
-      <c r="C56" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B57" s="2">
         <v>25003242</v>
       </c>
-      <c r="C57" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D57" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="B58" s="2">
         <v>25003264</v>
       </c>
-      <c r="C58" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D58" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B59" s="2">
         <v>25003221</v>
       </c>
-      <c r="C59" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D59" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B60" s="2">
         <v>25003257</v>
       </c>
-      <c r="C60" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B61" s="2">
         <v>25003311</v>
       </c>
-      <c r="C61" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="B62" s="2">
         <v>25003294</v>
       </c>
-      <c r="C62" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C62" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D62" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B63" s="2">
         <v>25003196</v>
       </c>
-      <c r="C63" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C63" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D63" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B64" s="2">
         <v>25003261</v>
       </c>
-      <c r="C64" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C64" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D64" s="2"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B65" s="2">
         <v>25003290</v>
       </c>
-      <c r="C65" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D65" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B66" s="2">
         <v>25003230</v>
       </c>
-      <c r="C66" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D66" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B67" s="2">
         <v>25003274</v>
       </c>
-      <c r="C67" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C67" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B68" s="2">
         <v>25003198</v>
       </c>
-      <c r="C68" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D68" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B69" s="2">
         <v>25003174</v>
       </c>
-      <c r="C69" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C69" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D69" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B70" s="2">
         <v>25007149</v>
       </c>
-      <c r="C70" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C70" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B71" s="2">
         <v>25003268</v>
       </c>
-      <c r="C71" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C71" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B72" s="2">
         <v>25003300</v>
       </c>
-      <c r="C72" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C72" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D72" s="5">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B73" s="2">
         <v>25003259</v>
       </c>
-      <c r="C73" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D73" s="2"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
         <v>82</v>
       </c>
       <c r="B74" s="2">
         <v>25003284</v>
       </c>
-      <c r="C74" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C74" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D74" s="2"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B75" s="2">
         <v>25003309</v>
       </c>
-      <c r="C75" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C75" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D75" s="2"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B76" s="2">
         <v>25003185</v>
       </c>
-      <c r="C76" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C76" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D76" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
         <v>85</v>
       </c>
       <c r="B77" s="2">
         <v>25003234</v>
       </c>
-      <c r="C77" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C77" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D77" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B78" s="2">
         <v>25003267</v>
       </c>
-      <c r="C78" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C78" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D78" s="5">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B79" s="2">
         <v>25003285</v>
       </c>
-      <c r="C79" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C79" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" s="2"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B80" s="2">
         <v>25003192</v>
       </c>
-      <c r="C80" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C80" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B81" s="2">
         <v>25003299</v>
       </c>
-      <c r="C81" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C81" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D81" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B82" s="2">
         <v>25003240</v>
       </c>
-      <c r="C82" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C82" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D82" s="2"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B83" s="2">
         <v>25003194</v>
       </c>
-      <c r="C83" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C83" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D83" s="2"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
         <v>92</v>
       </c>
       <c r="B84" s="2">
         <v>25003224</v>
       </c>
-      <c r="C84" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C84" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D84" s="2"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B85" s="2">
         <v>25003265</v>
       </c>
-      <c r="C85" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C85" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D85" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
         <v>94</v>
       </c>
       <c r="B86" s="2">
         <v>25003210</v>
       </c>
-      <c r="C86" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C86" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D86" s="2"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
         <v>95</v>
       </c>
       <c r="B87" s="2">
         <v>25003258</v>
       </c>
-      <c r="C87" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C87" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D87" s="2"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
         <v>96</v>
       </c>
       <c r="B88" s="2">
         <v>25003217</v>
       </c>
-      <c r="C88" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C88" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D88" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B89" s="2">
         <v>25003276</v>
       </c>
-      <c r="C89" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C89" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D89" s="2"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B90" s="2">
         <v>25003245</v>
       </c>
-      <c r="C90" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C90" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D90" s="2"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B91" s="2">
         <v>25003256</v>
       </c>
-      <c r="C91" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C91" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D91" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B92" s="2">
         <v>25003236</v>
       </c>
-      <c r="C92" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C92" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D92" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B93" s="2">
         <v>25003269</v>
       </c>
-      <c r="C93" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C93" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D93" s="2"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B94" s="2">
         <v>25003250</v>
       </c>
-      <c r="C94" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C94" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D94" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B95" s="2">
         <v>25003232</v>
       </c>
-      <c r="C95" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C95" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D95" s="2"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B96" s="2">
         <v>25003214</v>
       </c>
-      <c r="C96" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C96" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D96" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B97" s="2">
         <v>25003193</v>
       </c>
-      <c r="C97" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C97" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D97" s="2"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B98" s="2">
         <v>25003220</v>
       </c>
-      <c r="C98" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C98" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D98" s="2"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B99" s="2">
         <v>25003190</v>
       </c>
-      <c r="C99" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C99" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D99" s="2"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B100" s="2">
         <v>25003202</v>
       </c>
-      <c r="C100" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C100" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B101" s="2">
         <v>25003241</v>
       </c>
-      <c r="C101" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C101" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D101" s="2"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B102" s="2">
         <v>25003247</v>
       </c>
-      <c r="C102" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C102" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D102" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B103" s="2">
         <v>25003237</v>
       </c>
-      <c r="C103" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C103" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D103" s="2"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B104" s="2">
         <v>25003260</v>
       </c>
-      <c r="C104" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C104" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D104" s="2"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
         <v>113</v>
       </c>
       <c r="B105" s="2">
         <v>25003307</v>
       </c>
-      <c r="C105" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C105" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B106" s="2">
         <v>25003270</v>
       </c>
-      <c r="C106" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C106" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D106" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B107" s="2">
         <v>25003279</v>
       </c>
-      <c r="C107" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C107" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D107" s="2"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B108" s="2">
         <v>25003238</v>
       </c>
-      <c r="C108" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C108" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D108" s="2"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" s="2" t="s">
         <v>116</v>
       </c>
       <c r="B109" s="2">
         <v>25003275</v>
       </c>
-      <c r="C109" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C109" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D109" s="2"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B110" s="2">
         <v>25003255</v>
       </c>
-      <c r="C110" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C110" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D110" s="2"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B111" s="2">
         <v>25003304</v>
       </c>
-      <c r="C111" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C111" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D111" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B112" s="2">
         <v>25003233</v>
       </c>
-      <c r="C112" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C112" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D112" s="2"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B113" s="2">
         <v>25003262</v>
       </c>
-      <c r="C113" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C113" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D113" s="2"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A114" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B114" s="2">
         <v>25003271</v>
       </c>
-      <c r="C114" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C114" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D114" s="2"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B115" s="2">
         <v>25003266</v>
       </c>
-      <c r="C115" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C115" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D115" s="2"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A116" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B116" s="2">
         <v>25003231</v>
       </c>
-      <c r="C116" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C116" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D116" s="2"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A117" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B117" s="2">
         <v>25003312</v>
       </c>
-      <c r="C117" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C117" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D117" s="2"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B118" s="2">
         <v>25003254</v>
       </c>
-      <c r="C118" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C118" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D118" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A119" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B119" s="2">
         <v>25003296</v>
       </c>
-      <c r="C119" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C119" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D119" s="2"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A120" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B120" s="2">
         <v>25003295</v>
       </c>
-      <c r="C120" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C120" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D120" s="2"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A121" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B121" s="2">
         <v>25003249</v>
       </c>
-      <c r="C121" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C121" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D121" s="2"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A122" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B122" s="2">
         <v>25003282</v>
       </c>
-      <c r="C122" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C122" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D122" s="2"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A123" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B123" s="2">
         <v>25003310</v>
       </c>
-      <c r="C123" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C123" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D123" s="2"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A124" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B124" s="2">
         <v>25003272</v>
       </c>
-      <c r="C124" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C124" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D124" s="2"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A125" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B125" s="2">
         <v>25003291</v>
       </c>
-      <c r="C125" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C125" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D125" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A126" s="2" t="s">
         <v>134</v>
       </c>
       <c r="B126" s="2">
         <v>25003252</v>
       </c>
-      <c r="C126" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C126" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D126" s="2"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B127" s="2">
         <v>25003278</v>
       </c>
-      <c r="C127" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C127" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D127" s="2"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A128" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B128" s="2">
         <v>25003227</v>
       </c>
-      <c r="C128" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C128" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D128" s="2"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A129" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B129" s="2">
         <v>25003297</v>
       </c>
-      <c r="C129" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C129" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D129" s="2"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A130" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B130" s="2">
         <v>25003277</v>
       </c>
-      <c r="C130" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C130" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D130" s="2"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A131" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B131" s="2">
         <v>25003281</v>
       </c>
-      <c r="C131" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C131" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D131" s="2"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A132" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B132" s="2">
         <v>25003283</v>
       </c>
-      <c r="C132" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C132" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D132" s="2"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A133" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B133" s="2">
         <v>25003251</v>
       </c>
-      <c r="C133" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C133" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D133" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A134" s="2" t="s">
         <v>142</v>
       </c>
       <c r="B134" s="2">
         <v>25003306</v>
       </c>
-      <c r="C134" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C134" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D134" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A135" s="2" t="s">
         <v>143</v>
       </c>
       <c r="B135" s="2">
         <v>25003204</v>
       </c>
-      <c r="C135" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C135" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D135" s="2"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" s="2" t="s">
         <v>144</v>
       </c>
       <c r="B136" s="2">
         <v>25003263</v>
       </c>
-      <c r="C136" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C136" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D136" s="2"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A137" s="2" t="s">
         <v>145</v>
       </c>
       <c r="B137" s="2">
         <v>25003177</v>
       </c>
-      <c r="C137" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C137" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D137" s="2"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A138" s="2" t="s">
         <v>146</v>
       </c>
       <c r="B138" s="2">
         <v>25003211</v>
       </c>
-      <c r="C138" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C138" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D138" s="2"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A139" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B139" s="2">
         <v>25003308</v>
       </c>
-      <c r="C139" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C139" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D139" s="2"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A140" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B140" s="2">
         <v>25003175</v>
       </c>
-      <c r="C140" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C140" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D140" s="2"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A141" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B141" s="2">
         <v>25003305</v>
       </c>
-      <c r="C141" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C141" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D141" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A142" s="2" t="s">
         <v>150</v>
       </c>
       <c r="B142" s="2">
         <v>25003171</v>
       </c>
-      <c r="C142" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C142" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D142" s="2"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A143" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B143" s="2">
         <v>25003239</v>
       </c>
-      <c r="C143" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C143" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D143" s="2"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A144" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B144" s="2">
         <v>25003166</v>
       </c>
-      <c r="C144" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C144" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D144" s="2"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" s="2" t="s">
         <v>153</v>
       </c>
       <c r="B145" s="2">
         <v>25003173</v>
       </c>
-      <c r="C145" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C145" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D145" s="5">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A146" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B146" s="2">
         <v>25003235</v>
       </c>
-      <c r="C146" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C146" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D146" s="2"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A147" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B147" s="2">
         <v>25003287</v>
       </c>
-      <c r="C147" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C147" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D147" s="2"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A148" s="2" t="s">
         <v>156</v>
       </c>
       <c r="B148" s="2">
         <v>25003176</v>
       </c>
-      <c r="C148" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C148" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D148" s="2"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A149" s="2" t="s">
         <v>156</v>
       </c>
       <c r="B149" s="2">
         <v>25003186</v>
       </c>
-      <c r="C149" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C149" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D149" s="2"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A150" s="2" t="s">
         <v>157</v>
       </c>
       <c r="B150" s="2">
         <v>25003178</v>
       </c>
-      <c r="C150" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C150" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D150" s="5">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A151" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B151" s="2">
         <v>25003288</v>
       </c>
-      <c r="C151" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C151" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D151" s="2"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A152" s="2" t="s">
         <v>159</v>
       </c>
       <c r="B152" s="2">
         <v>25003203</v>
       </c>
-      <c r="C152" s="6" t="b">
-        <v>0</v>
-      </c>
+      <c r="C152" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D152" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B152">

--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="349" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BBD25DB-FEAB-45C6-95D4-ABB8C30357C1}"/>
+  <xr:revisionPtr revIDLastSave="397" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{576350ED-3991-4673-8098-F4B5F1ACF6CB}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Gas!$A$1:$D$152</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4333,7 +4332,7 @@
         <v>25003243</v>
       </c>
       <c r="C43" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" s="5">
         <v>46223</v>
@@ -4505,9 +4504,11 @@
         <v>25003292</v>
       </c>
       <c r="C56" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D56" s="5">
+        <v>46224</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
@@ -4545,11 +4546,9 @@
         <v>25003221</v>
       </c>
       <c r="C59" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D59" s="5">
-        <v>46224</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D59" s="5"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">

--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="397" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{576350ED-3991-4673-8098-F4B5F1ACF6CB}"/>
+  <xr:revisionPtr revIDLastSave="472" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{837F13BA-D686-4679-86CA-F8DC7EECE728}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
@@ -4044,9 +4044,11 @@
         <v>25003301</v>
       </c>
       <c r="C22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
@@ -4400,9 +4402,11 @@
         <v>25003205</v>
       </c>
       <c r="C48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D48" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
@@ -4412,9 +4416,11 @@
         <v>25003293</v>
       </c>
       <c r="C49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D49" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
@@ -4558,7 +4564,7 @@
         <v>25003257</v>
       </c>
       <c r="C60" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" s="5">
         <v>46224</v>
@@ -4756,9 +4762,11 @@
         <v>25003309</v>
       </c>
       <c r="C75" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D75" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D75" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
@@ -4810,9 +4818,11 @@
         <v>25003285</v>
       </c>
       <c r="C79" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D79" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D79" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
@@ -4822,9 +4832,11 @@
         <v>25003192</v>
       </c>
       <c r="C80" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D80" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D80" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
@@ -4848,9 +4860,11 @@
         <v>25003240</v>
       </c>
       <c r="C82" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D82" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D82" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
@@ -4860,9 +4874,11 @@
         <v>25003194</v>
       </c>
       <c r="C83" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D83" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D83" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
@@ -4872,9 +4888,11 @@
         <v>25003224</v>
       </c>
       <c r="C84" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D84" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D84" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
@@ -4910,9 +4928,11 @@
         <v>25003258</v>
       </c>
       <c r="C87" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D87" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D87" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
@@ -5014,9 +5034,11 @@
         <v>25003232</v>
       </c>
       <c r="C95" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D95" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D95" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
@@ -5040,9 +5062,11 @@
         <v>25003193</v>
       </c>
       <c r="C97" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D97" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D97" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
@@ -5114,9 +5138,11 @@
         <v>25003237</v>
       </c>
       <c r="C103" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D103" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D103" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
@@ -5126,9 +5152,11 @@
         <v>25003260</v>
       </c>
       <c r="C104" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D104" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D104" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
@@ -5138,9 +5166,11 @@
         <v>25003307</v>
       </c>
       <c r="C105" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D105" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D105" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
@@ -5164,9 +5194,11 @@
         <v>25003279</v>
       </c>
       <c r="C107" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D107" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D107" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
@@ -5188,9 +5220,11 @@
         <v>25003275</v>
       </c>
       <c r="C109" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D109" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D109" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
@@ -5200,9 +5234,11 @@
         <v>25003255</v>
       </c>
       <c r="C110" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D110" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D110" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
@@ -5226,9 +5262,11 @@
         <v>25003233</v>
       </c>
       <c r="C112" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D112" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D112" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
@@ -5238,9 +5276,11 @@
         <v>25003262</v>
       </c>
       <c r="C113" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D113" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D113" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A114" s="2" t="s">
@@ -5250,9 +5290,11 @@
         <v>25003271</v>
       </c>
       <c r="C114" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D114" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D114" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
@@ -5274,9 +5316,11 @@
         <v>25003231</v>
       </c>
       <c r="C116" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D116" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D116" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A117" s="2" t="s">
@@ -5286,9 +5330,11 @@
         <v>25003312</v>
       </c>
       <c r="C117" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D117" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D117" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" s="2" t="s">
@@ -5312,9 +5358,11 @@
         <v>25003296</v>
       </c>
       <c r="C119" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D119" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D119" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A120" s="2" t="s">
@@ -5324,9 +5372,11 @@
         <v>25003295</v>
       </c>
       <c r="C120" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D120" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D120" s="5">
+        <v>46227</v>
+      </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A121" s="2" t="s">
@@ -5336,9 +5386,11 @@
         <v>25003249</v>
       </c>
       <c r="C121" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D121" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D121" s="5">
+        <v>46227</v>
+      </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A122" s="2" t="s">
@@ -5348,9 +5400,11 @@
         <v>25003282</v>
       </c>
       <c r="C122" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D122" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D122" s="5">
+        <v>46227</v>
+      </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A123" s="2" t="s">
@@ -5360,9 +5414,11 @@
         <v>25003310</v>
       </c>
       <c r="C123" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D123" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D123" s="5">
+        <v>46227</v>
+      </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A124" s="2" t="s">
@@ -5410,9 +5466,11 @@
         <v>25003278</v>
       </c>
       <c r="C127" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D127" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D127" s="5">
+        <v>46225</v>
+      </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A128" s="2" t="s">
@@ -5446,9 +5504,11 @@
         <v>25003277</v>
       </c>
       <c r="C130" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D130" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D130" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A131" s="2" t="s">
@@ -5458,9 +5518,11 @@
         <v>25003281</v>
       </c>
       <c r="C131" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D131" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D131" s="5">
+        <v>46227</v>
+      </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A132" s="2" t="s">
@@ -5510,9 +5572,11 @@
         <v>25003204</v>
       </c>
       <c r="C135" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D135" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D135" s="5">
+        <v>46227</v>
+      </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" s="2" t="s">
@@ -5522,9 +5586,11 @@
         <v>25003263</v>
       </c>
       <c r="C136" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D136" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D136" s="5">
+        <v>46227</v>
+      </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A137" s="2" t="s">
@@ -5708,9 +5774,11 @@
         <v>25003288</v>
       </c>
       <c r="C151" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D151" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D151" s="5">
+        <v>46226</v>
+      </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A152" s="2" t="s">

--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="472" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{837F13BA-D686-4679-86CA-F8DC7EECE728}"/>
+  <xr:revisionPtr revIDLastSave="552" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AAD77DB-3D05-4133-ADE4-30E7DA682F36}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
@@ -3838,9 +3838,11 @@
         <v>25003172</v>
       </c>
       <c r="C7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
@@ -3864,9 +3866,11 @@
         <v>25003195</v>
       </c>
       <c r="C9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
@@ -4128,9 +4132,11 @@
         <v>25003303</v>
       </c>
       <c r="C28" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D28" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
@@ -4362,9 +4368,11 @@
         <v>25003246</v>
       </c>
       <c r="C45" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D45" s="5">
+        <v>46223</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
@@ -4470,9 +4478,11 @@
         <v>25003216</v>
       </c>
       <c r="C53" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D53" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D53" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
@@ -4552,9 +4562,11 @@
         <v>25003221</v>
       </c>
       <c r="C59" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D59" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="D59" s="5">
+        <v>46227</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
@@ -4578,9 +4590,11 @@
         <v>25003311</v>
       </c>
       <c r="C61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D61" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
@@ -4618,9 +4632,11 @@
         <v>25003261</v>
       </c>
       <c r="C64" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D64" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D64" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
@@ -4698,9 +4714,11 @@
         <v>25007149</v>
       </c>
       <c r="C70" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D70" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D70" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
@@ -4750,9 +4768,11 @@
         <v>25003284</v>
       </c>
       <c r="C74" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D74" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D74" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
@@ -4916,9 +4936,11 @@
         <v>25003210</v>
       </c>
       <c r="C86" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D86" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D86" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
@@ -4956,9 +4978,11 @@
         <v>25003276</v>
       </c>
       <c r="C89" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D89" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D89" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
@@ -5076,9 +5100,11 @@
         <v>25003220</v>
       </c>
       <c r="C98" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D98" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D98" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
@@ -5112,9 +5138,11 @@
         <v>25003241</v>
       </c>
       <c r="C101" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D101" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D101" s="5">
+        <v>46227</v>
+      </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
@@ -5428,9 +5456,11 @@
         <v>25003272</v>
       </c>
       <c r="C124" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D124" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D124" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A125" s="2" t="s">
@@ -5454,9 +5484,11 @@
         <v>25003252</v>
       </c>
       <c r="C126" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D126" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D126" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" s="2" t="s">
@@ -5480,9 +5512,11 @@
         <v>25003227</v>
       </c>
       <c r="C128" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D128" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D128" s="5">
+        <v>46227</v>
+      </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A129" s="2" t="s">
@@ -5532,9 +5566,11 @@
         <v>25003283</v>
       </c>
       <c r="C132" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D132" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D132" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A133" s="2" t="s">
@@ -5600,9 +5636,11 @@
         <v>25003177</v>
       </c>
       <c r="C137" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D137" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D137" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A138" s="2" t="s">
@@ -5612,9 +5650,11 @@
         <v>25003211</v>
       </c>
       <c r="C138" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D138" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D138" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A139" s="2" t="s">
@@ -5624,9 +5664,11 @@
         <v>25003308</v>
       </c>
       <c r="C139" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D139" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D139" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A140" s="2" t="s">
@@ -5636,9 +5678,11 @@
         <v>25003175</v>
       </c>
       <c r="C140" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D140" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D140" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A141" s="2" t="s">
@@ -5662,9 +5706,11 @@
         <v>25003171</v>
       </c>
       <c r="C142" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D142" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D142" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A143" s="2" t="s">
@@ -5674,9 +5720,11 @@
         <v>25003239</v>
       </c>
       <c r="C143" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D143" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D143" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A144" s="2" t="s">
@@ -5686,9 +5734,11 @@
         <v>25003166</v>
       </c>
       <c r="C144" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D144" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D144" s="5">
+        <v>46230</v>
+      </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" s="2" t="s">
@@ -5712,9 +5762,11 @@
         <v>25003235</v>
       </c>
       <c r="C146" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D146" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D146" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A147" s="2" t="s">
@@ -5724,9 +5776,11 @@
         <v>25003287</v>
       </c>
       <c r="C147" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D147" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D147" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A148" s="2" t="s">
@@ -5736,9 +5790,11 @@
         <v>25003176</v>
       </c>
       <c r="C148" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D148" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D148" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A149" s="2" t="s">
@@ -5748,9 +5804,11 @@
         <v>25003186</v>
       </c>
       <c r="C149" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D149" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D149" s="5">
+        <v>46231</v>
+      </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A150" s="2" t="s">
@@ -5788,9 +5846,11 @@
         <v>25003203</v>
       </c>
       <c r="C152" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D152" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D152" s="5">
+        <v>46230</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B152">

--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="552" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AAD77DB-3D05-4133-ADE4-30E7DA682F36}"/>
+  <xr:revisionPtr revIDLastSave="569" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E0AB989-8AE7-4D6E-956D-F5F14A52D07B}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
@@ -681,6 +681,10 @@
     </a>
   </bag>
 </FeaturePropertyBags>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4438,9 +4442,11 @@
         <v>25003223</v>
       </c>
       <c r="C50" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D50" s="5">
+        <v>46232</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
@@ -4992,9 +4998,11 @@
         <v>25003245</v>
       </c>
       <c r="C90" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D90" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D90" s="5">
+        <v>46232</v>
+      </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
@@ -5032,9 +5040,11 @@
         <v>25003269</v>
       </c>
       <c r="C93" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D93" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D93" s="5">
+        <v>46232</v>
+      </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
@@ -5114,9 +5124,11 @@
         <v>25003190</v>
       </c>
       <c r="C99" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D99" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D99" s="5">
+        <v>46232</v>
+      </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
@@ -5236,9 +5248,11 @@
         <v>25003238</v>
       </c>
       <c r="C108" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D108" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D108" s="5">
+        <v>46232</v>
+      </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" s="2" t="s">

--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="569" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E0AB989-8AE7-4D6E-956D-F5F14A52D07B}"/>
+  <xr:revisionPtr revIDLastSave="574" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7DF8B1F-A412-405E-B54B-CA6D943E8FAF}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
+    <workbookView xWindow="71880" yWindow="-8550" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
   <sheets>
     <sheet name="Elec" sheetId="1" r:id="rId1"/>
@@ -681,10 +681,6 @@
     </a>
   </bag>
 </FeaturePropertyBags>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4762,9 +4758,11 @@
         <v>25003259</v>
       </c>
       <c r="C73" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D73" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D73" s="5">
+        <v>46233</v>
+      </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">

--- a/data/Summer_Ridge_Master_Sheet.xlsx
+++ b/data/Summer_Ridge_Master_Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="574" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7DF8B1F-A412-405E-B54B-CA6D943E8FAF}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7E7F68D-79DF-4204-86D8-9FAFC9DE3510}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-8550" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
@@ -4146,9 +4146,11 @@
         <v>25003222</v>
       </c>
       <c r="C29" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D29" s="5">
+        <v>46234</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
